--- a/RESs data.xlsx
+++ b/RESs data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\default.LAPTOP-J6DGB5J8\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17E52F9-8822-4EEE-955A-80FCB296679C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B603C350-151F-4425-8C95-88D3A023E2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garver 6-bus" sheetId="1" r:id="rId1"/>
@@ -3819,8 +3819,8 @@
       <xdr:rowOff>16159</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606384" cy="178832"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -3922,7 +3922,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -4322,38 +4322,38 @@
         <v>1</v>
       </c>
       <c r="B5" s="9">
-        <v>3.7803345257662199E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="C5" s="9">
-        <v>5.8880402204389497E-2</v>
+        <v>0.13769999999999999</v>
       </c>
       <c r="D5" s="9">
-        <v>3.2775790389635497E-2</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="E5" s="9">
-        <v>6.3907957072416102E-2</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="F5" s="9">
-        <v>3.8963550227206802E-2</v>
+        <v>8.9200000000000002E-2</v>
       </c>
       <c r="G5" s="9">
-        <v>5.7720197234844797E-2</v>
+        <v>9.4E-2</v>
       </c>
       <c r="H5" s="9">
-        <v>0.185342743884753</v>
+        <v>0.14979999999999999</v>
       </c>
       <c r="I5" s="9">
-        <v>0.236875181282026</v>
+        <v>0.14130000000000001</v>
       </c>
       <c r="J5" s="9">
-        <v>0.16938992555351401</v>
+        <v>0.13039999999999999</v>
       </c>
       <c r="K5" s="10">
-        <v>0.11834090689355101</v>
+        <v>0.1138</v>
       </c>
       <c r="L5" s="13">
         <f>SUM(B5:K5)</f>
-        <v>0.99999999999999889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -6438,38 +6438,38 @@
         <v>1</v>
       </c>
       <c r="B5" s="9">
-        <v>3.3209291835814198E-2</v>
+        <v>0.1426</v>
       </c>
       <c r="C5" s="9">
-        <v>5.9652683806946299E-2</v>
+        <v>0.1133</v>
       </c>
       <c r="D5" s="9">
-        <v>1.9903022101939599E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="E5" s="9">
-        <v>2.9149751917005001E-2</v>
+        <v>8.77E-2</v>
       </c>
       <c r="F5" s="9">
-        <v>2.72327469553451E-2</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="G5" s="9">
-        <v>8.1867388362652199E-2</v>
+        <v>0.1119</v>
       </c>
       <c r="H5" s="9">
-        <v>8.4573748308525001E-2</v>
+        <v>0.10879999999999999</v>
       </c>
       <c r="I5" s="9">
-        <v>8.2713125845737506E-2</v>
+        <v>0.14169999999999999</v>
       </c>
       <c r="J5" s="9">
-        <v>0.166384754172305</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="K5" s="10">
-        <v>0.41531348669373003</v>
+        <v>6.2399999999999997E-2</v>
       </c>
       <c r="L5" s="13">
         <f>SUM(B5:K5)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
